--- a/Design Files/Xponent-tech/BOM/eSpark-BOM-Xponent-tech.xlsx
+++ b/Design Files/Xponent-tech/BOM/eSpark-BOM-Xponent-tech.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="318">
   <si>
     <t>Component list</t>
   </si>
@@ -1446,7 +1446,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1684,6 +1684,44 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2135,7 +2173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R61"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -4934,69 +4972,69 @@
     </row>
     <row r="59" spans="1:18" s="68" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="66"/>
-      <c r="B59" s="47">
+      <c r="B59" s="87">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C59" s="54" t="s">
+      <c r="C59" s="88" t="s">
         <v>312</v>
       </c>
-      <c r="D59" s="51" t="s">
+      <c r="D59" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="E59" s="51" t="s">
+      <c r="E59" s="59" t="s">
         <v>118</v>
       </c>
-      <c r="F59" s="51" t="s">
+      <c r="F59" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="G59" s="51" t="s">
+      <c r="G59" s="59" t="s">
         <v>180</v>
       </c>
-      <c r="H59" s="51" t="s">
+      <c r="H59" s="59" t="s">
         <v>199</v>
       </c>
-      <c r="I59" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J59" s="51" t="s">
+      <c r="I59" s="59" t="s">
+        <v>301</v>
+      </c>
+      <c r="J59" s="59" t="s">
         <v>299</v>
       </c>
-      <c r="K59" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="L59" s="51">
+      <c r="K59" s="59" t="s">
+        <v>301</v>
+      </c>
+      <c r="L59" s="59">
         <v>3</v>
       </c>
-      <c r="M59" s="51">
+      <c r="M59" s="59">
         <v>5</v>
       </c>
-      <c r="N59" s="64" t="s">
-        <v>300</v>
-      </c>
-      <c r="O59" s="52">
+      <c r="N59" s="89" t="s">
+        <v>300</v>
+      </c>
+      <c r="O59" s="90">
         <v>0.1139</v>
       </c>
-      <c r="P59" s="52">
+      <c r="P59" s="90">
         <f t="shared" ref="P59" si="24">O59*M59</f>
         <v>0.56950000000000001</v>
       </c>
-      <c r="Q59" s="51"/>
-      <c r="R59" s="39"/>
+      <c r="Q59" s="59"/>
+      <c r="R59" s="59"/>
     </row>
     <row r="60" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
-      <c r="B60" s="40"/>
-      <c r="C60" s="41"/>
-      <c r="D60" s="42"/>
-      <c r="E60" s="43"/>
-      <c r="F60" s="44"/>
-      <c r="G60" s="45"/>
-      <c r="H60" s="44"/>
-      <c r="I60" s="45"/>
-      <c r="J60" s="44"/>
-      <c r="K60" s="45"/>
-      <c r="L60" s="45"/>
+      <c r="B60" s="91"/>
+      <c r="C60" s="92"/>
+      <c r="D60" s="93"/>
+      <c r="E60" s="94"/>
+      <c r="F60" s="95"/>
+      <c r="G60" s="96"/>
+      <c r="H60" s="95"/>
+      <c r="I60" s="96"/>
+      <c r="J60" s="95"/>
+      <c r="K60" s="96"/>
+      <c r="L60" s="96"/>
       <c r="M60" s="81" t="s">
         <v>5</v>
       </c>
@@ -5006,41 +5044,15 @@
         <f>SUM(P10:P59)</f>
         <v>31.379900000000003</v>
       </c>
-      <c r="Q60" s="83"/>
-      <c r="R60" s="84"/>
-    </row>
-    <row r="61" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="1"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="10"/>
-      <c r="M61" s="81" t="s">
-        <v>6</v>
-      </c>
-      <c r="N61" s="82"/>
-      <c r="O61" s="82"/>
-      <c r="P61" s="49">
-        <f>P60/2</f>
-        <v>15.689950000000001</v>
-      </c>
-      <c r="Q61" s="85"/>
-      <c r="R61" s="86"/>
+      <c r="Q60" s="97"/>
+      <c r="R60" s="98"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="K1:R1"/>
     <mergeCell ref="R3:R8"/>
     <mergeCell ref="M60:O60"/>
-    <mergeCell ref="Q60:R61"/>
-    <mergeCell ref="M61:O61"/>
+    <mergeCell ref="Q60:R60"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="N10" r:id="rId1"/>
@@ -5104,7 +5116,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="29.85546875" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" customWidth="1"/>

--- a/Design Files/Xponent-tech/BOM/eSpark-BOM-Xponent-tech.xlsx
+++ b/Design Files/Xponent-tech/BOM/eSpark-BOM-Xponent-tech.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="328">
   <si>
     <t>Component list</t>
   </si>
@@ -975,6 +975,36 @@
   </si>
   <si>
     <t>Quantity per Board</t>
+  </si>
+  <si>
+    <t>R1, R10</t>
+  </si>
+  <si>
+    <t>Trimmer, Cermet, Rest 100 Kilohms, PCB, 25 Turns, Pwr-Rtg 0.5W, 3296 Series</t>
+  </si>
+  <si>
+    <t>3296W-1-104</t>
+  </si>
+  <si>
+    <t>BOCHEN(Chengdu Guosheng Tech)</t>
+  </si>
+  <si>
+    <t>C330435</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>Res Cermet Trimmer 500K Ohm 10% 1/2W 25(Elec)Turn</t>
+  </si>
+  <si>
+    <t>3296W-1-504</t>
+  </si>
+  <si>
+    <t>C330437</t>
   </si>
 </sst>
 </file>
@@ -986,7 +1016,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1150,6 +1180,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1446,7 +1483,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1654,38 +1691,6 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1718,10 +1723,48 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2206,14 +2249,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="78"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="87"/>
+      <c r="O1" s="87"/>
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+      <c r="R1" s="88"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2261,7 +2304,7 @@
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
-      <c r="R3" s="79"/>
+      <c r="R3" s="89"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2285,7 +2328,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="80"/>
+      <c r="R4" s="90"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2309,7 +2352,7 @@
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
-      <c r="R5" s="80"/>
+      <c r="R5" s="90"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2329,7 +2372,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
-      <c r="R6" s="80"/>
+      <c r="R6" s="90"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2349,7 +2392,7 @@
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
-      <c r="R7" s="80"/>
+      <c r="R7" s="90"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2369,7 +2412,7 @@
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
-      <c r="R8" s="80"/>
+      <c r="R8" s="90"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -4972,11 +5015,11 @@
     </row>
     <row r="59" spans="1:18" s="68" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="66"/>
-      <c r="B59" s="87">
+      <c r="B59" s="77">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C59" s="88" t="s">
+      <c r="C59" s="78" t="s">
         <v>312</v>
       </c>
       <c r="D59" s="59" t="s">
@@ -5009,13 +5052,13 @@
       <c r="M59" s="59">
         <v>5</v>
       </c>
-      <c r="N59" s="89" t="s">
-        <v>300</v>
-      </c>
-      <c r="O59" s="90">
+      <c r="N59" s="79" t="s">
+        <v>300</v>
+      </c>
+      <c r="O59" s="80">
         <v>0.1139</v>
       </c>
-      <c r="P59" s="90">
+      <c r="P59" s="80">
         <f t="shared" ref="P59" si="24">O59*M59</f>
         <v>0.56950000000000001</v>
       </c>
@@ -5024,28 +5067,28 @@
     </row>
     <row r="60" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
-      <c r="B60" s="91"/>
-      <c r="C60" s="92"/>
-      <c r="D60" s="93"/>
-      <c r="E60" s="94"/>
-      <c r="F60" s="95"/>
-      <c r="G60" s="96"/>
-      <c r="H60" s="95"/>
-      <c r="I60" s="96"/>
-      <c r="J60" s="95"/>
-      <c r="K60" s="96"/>
-      <c r="L60" s="96"/>
-      <c r="M60" s="81" t="s">
+      <c r="B60" s="81"/>
+      <c r="C60" s="82"/>
+      <c r="D60" s="83"/>
+      <c r="E60" s="84"/>
+      <c r="F60" s="85"/>
+      <c r="G60" s="86"/>
+      <c r="H60" s="85"/>
+      <c r="I60" s="86"/>
+      <c r="J60" s="85"/>
+      <c r="K60" s="86"/>
+      <c r="L60" s="86"/>
+      <c r="M60" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="N60" s="82"/>
-      <c r="O60" s="82"/>
+      <c r="N60" s="92"/>
+      <c r="O60" s="92"/>
       <c r="P60" s="48">
         <f>SUM(P10:P59)</f>
         <v>31.379900000000003</v>
       </c>
-      <c r="Q60" s="97"/>
-      <c r="R60" s="98"/>
+      <c r="Q60" s="93"/>
+      <c r="R60" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5146,15 +5189,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="78"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="87"/>
+      <c r="O1" s="87"/>
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+      <c r="R1" s="87"/>
+      <c r="S1" s="88"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -5204,7 +5247,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="79"/>
+      <c r="S3" s="89"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -5229,7 +5272,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="80"/>
+      <c r="S4" s="90"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -5254,7 +5297,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="80"/>
+      <c r="S5" s="90"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -5275,7 +5318,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="80"/>
+      <c r="S6" s="90"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -5296,7 +5339,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="80"/>
+      <c r="S7" s="90"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -5317,7 +5360,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="80"/>
+      <c r="S8" s="90"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -6440,7 +6483,7 @@
       <c r="R28" s="37"/>
       <c r="S28" s="59"/>
     </row>
-    <row r="29" spans="1:19" s="68" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" s="68" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A29" s="66"/>
       <c r="B29" s="47">
         <f t="shared" si="0"/>
@@ -8187,17 +8230,17 @@
       <c r="K60" s="45"/>
       <c r="L60" s="45"/>
       <c r="M60" s="45"/>
-      <c r="N60" s="81" t="s">
+      <c r="N60" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="O60" s="82"/>
-      <c r="P60" s="82"/>
+      <c r="O60" s="92"/>
+      <c r="P60" s="92"/>
       <c r="Q60" s="48">
         <f>SUM(Q10:Q59)</f>
         <v>38.7821</v>
       </c>
-      <c r="R60" s="83"/>
-      <c r="S60" s="84"/>
+      <c r="R60" s="95"/>
+      <c r="S60" s="96"/>
     </row>
     <row r="61" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
@@ -8213,17 +8256,17 @@
       <c r="K61" s="10"/>
       <c r="L61" s="10"/>
       <c r="M61" s="10"/>
-      <c r="N61" s="81" t="s">
+      <c r="N61" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="O61" s="82"/>
-      <c r="P61" s="82"/>
+      <c r="O61" s="92"/>
+      <c r="P61" s="92"/>
       <c r="Q61" s="49">
         <f>Q60/2</f>
         <v>19.39105</v>
       </c>
-      <c r="R61" s="85"/>
-      <c r="S61" s="86"/>
+      <c r="R61" s="97"/>
+      <c r="S61" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -8292,7 +8335,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -8326,15 +8369,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="78"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="87"/>
+      <c r="O1" s="87"/>
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+      <c r="R1" s="87"/>
+      <c r="S1" s="88"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -8384,7 +8427,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="79"/>
+      <c r="S3" s="89"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -8409,7 +8452,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="80"/>
+      <c r="S4" s="90"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -8434,7 +8477,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="80"/>
+      <c r="S5" s="90"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -8455,7 +8498,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="80"/>
+      <c r="S6" s="90"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -8476,7 +8519,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="80"/>
+      <c r="S7" s="90"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -8497,7 +8540,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="80"/>
+      <c r="S8" s="90"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -8565,7 +8608,7 @@
       <c r="C10" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="99" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="37" t="s">
@@ -8615,13 +8658,13 @@
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B59" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B60" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="51" t="s">
+      <c r="D11" s="100" t="s">
         <v>19</v>
       </c>
       <c r="E11" s="51" t="s">
@@ -8677,7 +8720,7 @@
       <c r="C12" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="37" t="s">
+      <c r="D12" s="99" t="s">
         <v>20</v>
       </c>
       <c r="E12" s="37" t="s">
@@ -8733,7 +8776,7 @@
       <c r="C13" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="51" t="s">
+      <c r="D13" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="51" t="s">
@@ -8789,7 +8832,7 @@
       <c r="C14" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="99" t="s">
         <v>22</v>
       </c>
       <c r="E14" s="37" t="s">
@@ -8845,7 +8888,7 @@
       <c r="C15" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="51" t="s">
+      <c r="D15" s="100" t="s">
         <v>23</v>
       </c>
       <c r="E15" s="51" t="s">
@@ -8901,7 +8944,7 @@
       <c r="C16" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D16" s="99" t="s">
         <v>24</v>
       </c>
       <c r="E16" s="37" t="s">
@@ -8957,7 +9000,7 @@
       <c r="C17" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="51" t="s">
+      <c r="D17" s="100" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="51" t="s">
@@ -9013,7 +9056,7 @@
       <c r="C18" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="D18" s="99" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="37" t="s">
@@ -9069,7 +9112,7 @@
       <c r="C19" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="51" t="s">
+      <c r="D19" s="100" t="s">
         <v>27</v>
       </c>
       <c r="E19" s="51" t="s">
@@ -9125,7 +9168,7 @@
       <c r="C20" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D20" s="99" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="37" t="s">
@@ -9181,7 +9224,7 @@
       <c r="C21" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="51" t="s">
+      <c r="D21" s="100" t="s">
         <v>29</v>
       </c>
       <c r="E21" s="51" t="s">
@@ -9237,7 +9280,7 @@
       <c r="C22" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="37" t="s">
+      <c r="D22" s="99" t="s">
         <v>30</v>
       </c>
       <c r="E22" s="37" t="s">
@@ -9293,7 +9336,7 @@
       <c r="C23" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="51" t="s">
+      <c r="D23" s="100" t="s">
         <v>31</v>
       </c>
       <c r="E23" s="51" t="s">
@@ -9508,58 +9551,58 @@
       <c r="R26" s="37"/>
       <c r="S26" s="59"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="47">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C27" s="54" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>35</v>
+        <v>318</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>86</v>
+        <v>319</v>
       </c>
       <c r="F27" s="51" t="s">
         <v>298</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>149</v>
+        <v>320</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>194</v>
+        <v>321</v>
       </c>
       <c r="I27" s="51" t="s">
         <v>301</v>
       </c>
       <c r="J27" s="51" t="s">
-        <v>212</v>
+        <v>322</v>
       </c>
       <c r="K27" s="51" t="s">
         <v>256</v>
       </c>
       <c r="L27" s="51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M27" s="51">
         <f t="shared" ref="M27" si="17">L27*5</f>
+        <v>10</v>
+      </c>
+      <c r="N27" s="51">
         <v>15</v>
       </c>
-      <c r="N27" s="51">
-        <v>20</v>
-      </c>
       <c r="O27" s="64" t="s">
         <v>300</v>
       </c>
       <c r="P27" s="52">
-        <v>0.14399999999999999</v>
+        <v>0.30580000000000002</v>
       </c>
       <c r="Q27" s="52">
         <f t="shared" ref="Q27" si="18">P27*N27</f>
-        <v>2.88</v>
+        <v>4.5870000000000006</v>
       </c>
       <c r="R27" s="51"/>
       <c r="S27" s="59"/>
@@ -9630,7 +9673,7 @@
         <v>14</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>37</v>
+        <v>323</v>
       </c>
       <c r="E29" s="51" t="s">
         <v>88</v>
@@ -9654,14 +9697,14 @@
         <v>258</v>
       </c>
       <c r="L29" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M29" s="51">
         <f t="shared" ref="M29" si="19">L29*5</f>
+        <v>5</v>
+      </c>
+      <c r="N29" s="51">
         <v>10</v>
-      </c>
-      <c r="N29" s="51">
-        <v>20</v>
       </c>
       <c r="O29" s="64" t="s">
         <v>300</v>
@@ -9671,7 +9714,7 @@
       </c>
       <c r="Q29" s="52">
         <f t="shared" ref="Q29" si="20">P29*N29</f>
-        <v>1.51</v>
+        <v>0.755</v>
       </c>
       <c r="R29" s="51"/>
       <c r="S29" s="59"/>
@@ -9844,1574 +9887,1627 @@
       <c r="R32" s="37"/>
       <c r="S32" s="59"/>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="47">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
+      <c r="B33" s="46"/>
       <c r="C33" s="54" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>41</v>
+        <v>324</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>92</v>
+        <v>325</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>127</v>
+        <v>298</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>155</v>
+        <v>326</v>
       </c>
       <c r="H33" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="I33" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="I33" s="37" t="s">
         <v>301</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>218</v>
+        <v>327</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L33" s="51">
-        <v>2</v>
-      </c>
-      <c r="M33" s="51">
-        <f t="shared" ref="M33" si="23">L33*5</f>
+        <v>1</v>
+      </c>
+      <c r="M33" s="37">
+        <f t="shared" ref="M33:M34" si="23">L33*5</f>
+        <v>5</v>
+      </c>
+      <c r="N33" s="37">
         <v>10</v>
       </c>
-      <c r="N33" s="51">
-        <v>20</v>
-      </c>
-      <c r="O33" s="64" t="s">
-        <v>300</v>
-      </c>
-      <c r="P33" s="52">
-        <v>2.9600000000000001E-2</v>
-      </c>
-      <c r="Q33" s="52">
-        <f t="shared" ref="Q33" si="24">P33*N33</f>
-        <v>0.59200000000000008</v>
-      </c>
-      <c r="R33" s="51"/>
+      <c r="O33" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="P33" s="38">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="Q33" s="38">
+        <f>P33*N33</f>
+        <v>3.4499999999999997</v>
+      </c>
+      <c r="R33" s="37"/>
       <c r="S33" s="59"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="46">
-        <f>ROW(B34) - ROW($B$9)</f>
+      <c r="B34" s="47">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="53" t="s">
+      <c r="C34" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="37" t="s">
+      <c r="D34" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="F34" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="G34" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="H34" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="I34" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J34" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="K34" s="51" t="s">
+        <v>262</v>
+      </c>
+      <c r="L34" s="51">
+        <v>2</v>
+      </c>
+      <c r="M34" s="37">
+        <f t="shared" si="23"/>
+        <v>10</v>
+      </c>
+      <c r="N34" s="51">
+        <v>20</v>
+      </c>
+      <c r="O34" s="64" t="s">
+        <v>300</v>
+      </c>
+      <c r="P34" s="52">
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="Q34" s="52">
+        <f t="shared" ref="Q34" si="24">P34*N34</f>
+        <v>0.59200000000000008</v>
+      </c>
+      <c r="R34" s="51"/>
+      <c r="S34" s="59"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="46">
+        <f>ROW(B35) - ROW($B$9)</f>
+        <v>26</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="E34" s="37" t="s">
+      <c r="E35" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="F34" s="37" t="s">
+      <c r="F35" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="G34" s="37" t="s">
+      <c r="G35" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="H34" s="37" t="s">
+      <c r="H35" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I34" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="J34" s="37" t="s">
+      <c r="I35" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="J35" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="K34" s="37" t="s">
+      <c r="K35" s="37" t="s">
         <v>263</v>
       </c>
-      <c r="L34" s="37">
+      <c r="L35" s="37">
         <v>1</v>
       </c>
-      <c r="M34" s="37">
-        <f>L34*5</f>
+      <c r="M35" s="37">
+        <f>L35*5</f>
         <v>5</v>
       </c>
-      <c r="N34" s="37">
+      <c r="N35" s="37">
         <v>20</v>
       </c>
-      <c r="O34" s="63" t="s">
-        <v>300</v>
-      </c>
-      <c r="P34" s="38">
+      <c r="O35" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="P35" s="38">
         <v>2.7199999999999998E-2</v>
       </c>
-      <c r="Q34" s="38">
-        <f>P34*N34</f>
+      <c r="Q35" s="38">
+        <f>P35*N35</f>
         <v>0.54399999999999993</v>
       </c>
-      <c r="R34" s="37"/>
-      <c r="S34" s="59"/>
-    </row>
-    <row r="35" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="47">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="C35" s="54" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="51" t="s">
-        <v>43</v>
-      </c>
-      <c r="E35" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F35" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="G35" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="H35" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="I35" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J35" s="51" t="s">
-        <v>220</v>
-      </c>
-      <c r="K35" s="51" t="s">
-        <v>264</v>
-      </c>
-      <c r="L35" s="51">
-        <v>2</v>
-      </c>
-      <c r="M35" s="51">
-        <f t="shared" ref="M35" si="25">L35*5</f>
-        <v>10</v>
-      </c>
-      <c r="N35" s="51">
-        <v>50</v>
-      </c>
-      <c r="O35" s="64" t="s">
-        <v>300</v>
-      </c>
-      <c r="P35" s="52">
-        <v>8.3000000000000001E-3</v>
-      </c>
-      <c r="Q35" s="52">
-        <f t="shared" ref="Q35" si="26">P35*N35</f>
-        <v>0.41499999999999998</v>
-      </c>
-      <c r="R35" s="51"/>
+      <c r="R35" s="37"/>
       <c r="S35" s="59"/>
     </row>
     <row r="36" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="46">
-        <f>ROW(B36) - ROW($B$9)</f>
+      <c r="B36" s="47">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="53" t="s">
+      <c r="C36" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="G36" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="H36" s="37" t="s">
+      <c r="D36" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="H36" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="I36" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="J36" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="K36" s="37" t="s">
-        <v>265</v>
-      </c>
-      <c r="L36" s="37">
-        <v>3</v>
-      </c>
-      <c r="M36" s="37">
-        <f>L36*5</f>
-        <v>15</v>
-      </c>
-      <c r="N36" s="37">
-        <v>20</v>
-      </c>
-      <c r="O36" s="63" t="s">
-        <v>300</v>
-      </c>
-      <c r="P36" s="38">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="Q36" s="38">
-        <f>P36*N36</f>
-        <v>0.85999999999999988</v>
-      </c>
-      <c r="R36" s="37"/>
+      <c r="I36" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J36" s="51" t="s">
+        <v>220</v>
+      </c>
+      <c r="K36" s="51" t="s">
+        <v>264</v>
+      </c>
+      <c r="L36" s="51">
+        <v>2</v>
+      </c>
+      <c r="M36" s="51">
+        <f t="shared" ref="M36" si="25">L36*5</f>
+        <v>10</v>
+      </c>
+      <c r="N36" s="51">
+        <v>50</v>
+      </c>
+      <c r="O36" s="64" t="s">
+        <v>300</v>
+      </c>
+      <c r="P36" s="52">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="Q36" s="52">
+        <f t="shared" ref="Q36" si="26">P36*N36</f>
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="R36" s="51"/>
       <c r="S36" s="59"/>
     </row>
     <row r="37" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="47">
-        <f t="shared" si="0"/>
+      <c r="B37" s="46">
+        <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="54" t="s">
+      <c r="C37" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="E37" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="F37" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="G37" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="H37" s="51" t="s">
+      <c r="D37" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="G37" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="H37" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="I37" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J37" s="51" t="s">
-        <v>222</v>
-      </c>
-      <c r="K37" s="51" t="s">
-        <v>266</v>
-      </c>
-      <c r="L37" s="51">
-        <v>2</v>
-      </c>
-      <c r="M37" s="51">
-        <f t="shared" ref="M37" si="27">L37*5</f>
-        <v>10</v>
-      </c>
-      <c r="N37" s="51">
+      <c r="I37" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="J37" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="K37" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="L37" s="37">
+        <v>3</v>
+      </c>
+      <c r="M37" s="37">
+        <f>L37*5</f>
+        <v>15</v>
+      </c>
+      <c r="N37" s="37">
         <v>20</v>
       </c>
-      <c r="O37" s="64" t="s">
-        <v>300</v>
-      </c>
-      <c r="P37" s="52">
-        <v>2.5100000000000001E-2</v>
-      </c>
-      <c r="Q37" s="52">
-        <f t="shared" ref="Q37" si="28">P37*N37</f>
-        <v>0.502</v>
-      </c>
-      <c r="R37" s="51"/>
+      <c r="O37" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="P37" s="38">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="Q37" s="38">
+        <f>P37*N37</f>
+        <v>0.85999999999999988</v>
+      </c>
+      <c r="R37" s="37"/>
       <c r="S37" s="59"/>
     </row>
     <row r="38" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="46">
-        <f>ROW(B38) - ROW($B$9)</f>
+      <c r="B38" s="47">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="53" t="s">
+      <c r="C38" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="37" t="s">
+      <c r="D38" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="F38" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="G38" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="H38" s="51" t="s">
+        <v>196</v>
+      </c>
+      <c r="I38" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J38" s="51" t="s">
+        <v>222</v>
+      </c>
+      <c r="K38" s="51" t="s">
+        <v>266</v>
+      </c>
+      <c r="L38" s="51">
+        <v>2</v>
+      </c>
+      <c r="M38" s="51">
+        <f t="shared" ref="M38" si="27">L38*5</f>
+        <v>10</v>
+      </c>
+      <c r="N38" s="51">
+        <v>20</v>
+      </c>
+      <c r="O38" s="64" t="s">
+        <v>300</v>
+      </c>
+      <c r="P38" s="52">
+        <v>2.5100000000000001E-2</v>
+      </c>
+      <c r="Q38" s="52">
+        <f t="shared" ref="Q38" si="28">P38*N38</f>
+        <v>0.502</v>
+      </c>
+      <c r="R38" s="51"/>
+      <c r="S38" s="59"/>
+    </row>
+    <row r="39" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="46">
+        <f>ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="E38" s="37" t="s">
+      <c r="E39" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="F38" s="37" t="s">
+      <c r="F39" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="G38" s="37" t="s">
+      <c r="G39" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="H38" s="37" t="s">
+      <c r="H39" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="I38" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="J38" s="37" t="s">
+      <c r="I39" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="J39" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="K38" s="37" t="s">
+      <c r="K39" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="L38" s="37">
+      <c r="L39" s="37">
         <v>3</v>
       </c>
-      <c r="M38" s="37">
-        <f>L38*5</f>
+      <c r="M39" s="37">
+        <f>L39*5</f>
         <v>15</v>
       </c>
-      <c r="N38" s="37">
+      <c r="N39" s="37">
         <v>20</v>
       </c>
-      <c r="O38" s="63" t="s">
-        <v>300</v>
-      </c>
-      <c r="P38" s="38">
+      <c r="O39" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="P39" s="38">
         <v>2.86E-2</v>
       </c>
-      <c r="Q38" s="38">
-        <f>P38*N38</f>
+      <c r="Q39" s="38">
+        <f>P39*N39</f>
         <v>0.57200000000000006</v>
       </c>
-      <c r="R38" s="37"/>
-      <c r="S38" s="59"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="B39" s="47">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="C39" s="54" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="51" t="s">
-        <v>47</v>
-      </c>
-      <c r="E39" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="F39" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="G39" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="H39" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="I39" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J39" s="51" t="s">
-        <v>224</v>
-      </c>
-      <c r="K39" s="51" t="s">
-        <v>268</v>
-      </c>
-      <c r="L39" s="51">
-        <v>2</v>
-      </c>
-      <c r="M39" s="51">
-        <f t="shared" ref="M39" si="29">L39*5</f>
-        <v>10</v>
-      </c>
-      <c r="N39" s="51">
-        <v>50</v>
-      </c>
-      <c r="O39" s="64" t="s">
-        <v>300</v>
-      </c>
-      <c r="P39" s="52">
-        <v>8.2000000000000007E-3</v>
-      </c>
-      <c r="Q39" s="52">
-        <f t="shared" ref="Q39" si="30">P39*N39</f>
-        <v>0.41000000000000003</v>
-      </c>
-      <c r="R39" s="51"/>
+      <c r="R39" s="37"/>
       <c r="S39" s="59"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="46">
-        <f>ROW(B40) - ROW($B$9)</f>
+      <c r="B40" s="47">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="53" t="s">
+      <c r="C40" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="F40" s="37" t="s">
+      <c r="D40" s="100" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="F40" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="G40" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="H40" s="37" t="s">
+      <c r="G40" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="H40" s="51" t="s">
         <v>184</v>
       </c>
-      <c r="I40" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="J40" s="37" t="s">
-        <v>225</v>
-      </c>
-      <c r="K40" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="L40" s="37">
-        <v>3</v>
-      </c>
-      <c r="M40" s="37">
-        <f>L40*5</f>
-        <v>15</v>
-      </c>
-      <c r="N40" s="37">
-        <v>20</v>
-      </c>
-      <c r="O40" s="63" t="s">
-        <v>300</v>
-      </c>
-      <c r="P40" s="38">
-        <v>2.98E-2</v>
-      </c>
-      <c r="Q40" s="38">
-        <f>P40*N40</f>
-        <v>0.59599999999999997</v>
-      </c>
-      <c r="R40" s="37"/>
+      <c r="I40" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J40" s="51" t="s">
+        <v>224</v>
+      </c>
+      <c r="K40" s="51" t="s">
+        <v>268</v>
+      </c>
+      <c r="L40" s="51">
+        <v>2</v>
+      </c>
+      <c r="M40" s="51">
+        <f t="shared" ref="M40" si="29">L40*5</f>
+        <v>10</v>
+      </c>
+      <c r="N40" s="51">
+        <v>50</v>
+      </c>
+      <c r="O40" s="64" t="s">
+        <v>300</v>
+      </c>
+      <c r="P40" s="52">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="Q40" s="52">
+        <f t="shared" ref="Q40" si="30">P40*N40</f>
+        <v>0.41000000000000003</v>
+      </c>
+      <c r="R40" s="51"/>
       <c r="S40" s="59"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="47">
-        <f t="shared" si="0"/>
+      <c r="B41" s="46">
+        <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="54"/>
-      <c r="D41" s="51" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="F41" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="G41" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="H41" s="51" t="s">
+      <c r="C41" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="G41" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="H41" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I41" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J41" s="51" t="s">
-        <v>226</v>
-      </c>
-      <c r="K41" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="L41" s="51">
+      <c r="I41" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="J41" s="37" t="s">
+        <v>225</v>
+      </c>
+      <c r="K41" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="L41" s="37">
         <v>3</v>
       </c>
-      <c r="M41" s="51">
-        <f t="shared" ref="M41" si="31">L41*5</f>
+      <c r="M41" s="37">
+        <f>L41*5</f>
         <v>15</v>
       </c>
-      <c r="N41" s="51">
-        <v>100</v>
-      </c>
-      <c r="O41" s="64" t="s">
-        <v>300</v>
-      </c>
-      <c r="P41" s="52">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="Q41" s="52">
-        <f t="shared" ref="Q41" si="32">P41*N41</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R41" s="51"/>
+      <c r="N41" s="37">
+        <v>20</v>
+      </c>
+      <c r="O41" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="P41" s="38">
+        <v>2.98E-2</v>
+      </c>
+      <c r="Q41" s="38">
+        <f>P41*N41</f>
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="R41" s="37"/>
       <c r="S41" s="59"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="46">
-        <f>ROW(B42) - ROW($B$9)</f>
+      <c r="B42" s="47">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="53" t="s">
+      <c r="C42" s="54"/>
+      <c r="D42" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="F42" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="G42" s="51" t="s">
+        <v>163</v>
+      </c>
+      <c r="H42" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="I42" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J42" s="51" t="s">
+        <v>226</v>
+      </c>
+      <c r="K42" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="L42" s="51">
+        <v>3</v>
+      </c>
+      <c r="M42" s="51">
+        <f t="shared" ref="M42" si="31">L42*5</f>
+        <v>15</v>
+      </c>
+      <c r="N42" s="51">
+        <v>100</v>
+      </c>
+      <c r="O42" s="64" t="s">
+        <v>300</v>
+      </c>
+      <c r="P42" s="52">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q42" s="52">
+        <f t="shared" ref="Q42" si="32">P42*N42</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R42" s="51"/>
+      <c r="S42" s="59"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="46">
+        <f>ROW(B43) - ROW($B$9)</f>
+        <v>34</v>
+      </c>
+      <c r="C43" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="D42" s="37" t="s">
+      <c r="D43" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="E42" s="37" t="s">
+      <c r="E43" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="F42" s="37" t="s">
+      <c r="F43" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="G42" s="37" t="s">
+      <c r="G43" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="H42" s="37" t="s">
+      <c r="H43" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I42" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="J42" s="37" t="s">
+      <c r="I43" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="J43" s="37" t="s">
         <v>227</v>
       </c>
-      <c r="K42" s="37" t="s">
+      <c r="K43" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="L42" s="37">
+      <c r="L43" s="37">
         <v>2</v>
       </c>
-      <c r="M42" s="37">
-        <f>L42*5</f>
+      <c r="M43" s="37">
+        <f>L43*5</f>
         <v>10</v>
       </c>
-      <c r="N42" s="37">
+      <c r="N43" s="37">
         <v>100</v>
       </c>
-      <c r="O42" s="63" t="s">
-        <v>300</v>
-      </c>
-      <c r="P42" s="38">
+      <c r="O43" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="P43" s="38">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q42" s="38">
-        <f>P42*N42</f>
+      <c r="Q43" s="38">
+        <f>P43*N43</f>
         <v>0.12</v>
       </c>
-      <c r="R42" s="37"/>
-      <c r="S42" s="59"/>
-    </row>
-    <row r="43" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="47">
+      <c r="R43" s="37"/>
+      <c r="S43" s="59"/>
+    </row>
+    <row r="44" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="47">
         <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="C43" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="51" t="s">
+      <c r="D44" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="E43" s="51" t="s">
+      <c r="E44" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="F43" s="51" t="s">
+      <c r="F44" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="G43" s="51" t="s">
+      <c r="G44" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="H43" s="51" t="s">
+      <c r="H44" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="I43" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J43" s="51" t="s">
+      <c r="I44" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J44" s="51" t="s">
         <v>228</v>
       </c>
-      <c r="K43" s="51" t="s">
+      <c r="K44" s="51" t="s">
         <v>272</v>
       </c>
-      <c r="L43" s="51">
+      <c r="L44" s="51">
         <v>3</v>
       </c>
-      <c r="M43" s="51">
-        <f t="shared" ref="M43" si="33">L43*5</f>
+      <c r="M44" s="51">
+        <f t="shared" ref="M44" si="33">L44*5</f>
         <v>15</v>
       </c>
-      <c r="N43" s="51">
+      <c r="N44" s="51">
         <v>20</v>
       </c>
-      <c r="O43" s="64" t="s">
-        <v>300</v>
-      </c>
-      <c r="P43" s="52">
+      <c r="O44" s="64" t="s">
+        <v>300</v>
+      </c>
+      <c r="P44" s="52">
         <v>2.7199999999999998E-2</v>
       </c>
-      <c r="Q43" s="52">
-        <f t="shared" ref="Q43" si="34">P43*N43</f>
+      <c r="Q44" s="52">
+        <f t="shared" ref="Q44" si="34">P44*N44</f>
         <v>0.54399999999999993</v>
       </c>
-      <c r="R43" s="51"/>
-      <c r="S43" s="59"/>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
-      <c r="B44" s="46">
-        <f>ROW(B44) - ROW($B$9)</f>
-        <v>35</v>
-      </c>
-      <c r="C44" s="53" t="s">
+      <c r="R44" s="51"/>
+      <c r="S44" s="59"/>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="46">
+        <f>ROW(B45) - ROW($B$9)</f>
+        <v>36</v>
+      </c>
+      <c r="C45" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="D44" s="37" t="s">
+      <c r="D45" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="E44" s="37" t="s">
+      <c r="E45" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="F44" s="37" t="s">
+      <c r="F45" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="G44" s="37" t="s">
+      <c r="G45" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="H44" s="37" t="s">
+      <c r="H45" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I44" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="J44" s="37" t="s">
+      <c r="I45" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="J45" s="37" t="s">
         <v>229</v>
       </c>
-      <c r="K44" s="37" t="s">
+      <c r="K45" s="37" t="s">
         <v>273</v>
       </c>
-      <c r="L44" s="37">
+      <c r="L45" s="37">
         <v>2</v>
       </c>
-      <c r="M44" s="37">
-        <f>L44*5</f>
+      <c r="M45" s="37">
+        <f>L45*5</f>
         <v>10</v>
       </c>
-      <c r="N44" s="37">
+      <c r="N45" s="37">
         <v>20</v>
       </c>
-      <c r="O44" s="63" t="s">
-        <v>300</v>
-      </c>
-      <c r="P44" s="38">
+      <c r="O45" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="P45" s="38">
         <v>2.4899999999999999E-2</v>
       </c>
-      <c r="Q44" s="38">
-        <f>P44*N44</f>
+      <c r="Q45" s="38">
+        <f>P45*N45</f>
         <v>0.498</v>
       </c>
-      <c r="R44" s="37"/>
-      <c r="S44" s="59"/>
-    </row>
-    <row r="45" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
-      <c r="B45" s="47">
+      <c r="R45" s="37"/>
+      <c r="S45" s="59"/>
+    </row>
+    <row r="46" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="47">
         <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="C45" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D45" s="51" t="s">
+      <c r="D46" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="E45" s="51" t="s">
+      <c r="E46" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="F45" s="51" t="s">
+      <c r="F46" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="G45" s="51" t="s">
+      <c r="G46" s="51" t="s">
         <v>167</v>
       </c>
-      <c r="H45" s="51" t="s">
+      <c r="H46" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="I45" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J45" s="51" t="s">
+      <c r="I46" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J46" s="51" t="s">
         <v>230</v>
       </c>
-      <c r="K45" s="51" t="s">
+      <c r="K46" s="51" t="s">
         <v>274</v>
       </c>
-      <c r="L45" s="51">
+      <c r="L46" s="51">
         <v>3</v>
       </c>
-      <c r="M45" s="51">
-        <f t="shared" ref="M45" si="35">L45*5</f>
+      <c r="M46" s="51">
+        <f t="shared" ref="M46" si="35">L46*5</f>
         <v>15</v>
       </c>
-      <c r="N45" s="51">
+      <c r="N46" s="51">
         <v>20</v>
       </c>
-      <c r="O45" s="64" t="s">
-        <v>300</v>
-      </c>
-      <c r="P45" s="52">
+      <c r="O46" s="64" t="s">
+        <v>300</v>
+      </c>
+      <c r="P46" s="52">
         <v>3.0200000000000001E-2</v>
       </c>
-      <c r="Q45" s="52">
-        <f t="shared" ref="Q45" si="36">P45*N45</f>
+      <c r="Q46" s="52">
+        <f t="shared" ref="Q46" si="36">P46*N46</f>
         <v>0.60399999999999998</v>
       </c>
-      <c r="R45" s="51"/>
-      <c r="S45" s="59"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
-      <c r="B46" s="46">
-        <f>ROW(B46) - ROW($B$9)</f>
-        <v>37</v>
-      </c>
-      <c r="C46" s="53" t="s">
+      <c r="R46" s="51"/>
+      <c r="S46" s="59"/>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="46">
+        <f>ROW(B47) - ROW($B$9)</f>
+        <v>38</v>
+      </c>
+      <c r="C47" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="D46" s="37" t="s">
+      <c r="D47" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="E46" s="37" t="s">
+      <c r="E47" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="F46" s="37" t="s">
+      <c r="F47" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="G46" s="37" t="s">
+      <c r="G47" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="H46" s="37" t="s">
+      <c r="H47" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I46" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="J46" s="37" t="s">
+      <c r="I47" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="J47" s="37" t="s">
         <v>231</v>
       </c>
-      <c r="K46" s="37" t="s">
+      <c r="K47" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="L46" s="37">
+      <c r="L47" s="37">
         <v>2</v>
       </c>
-      <c r="M46" s="37">
-        <f>L46*5</f>
+      <c r="M47" s="37">
+        <f>L47*5</f>
         <v>10</v>
       </c>
-      <c r="N46" s="37">
+      <c r="N47" s="37">
         <v>20</v>
       </c>
-      <c r="O46" s="63" t="s">
-        <v>300</v>
-      </c>
-      <c r="P46" s="38">
+      <c r="O47" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="P47" s="38">
         <v>2.7799999999999998E-2</v>
       </c>
-      <c r="Q46" s="38">
-        <f>P46*N46</f>
+      <c r="Q47" s="38">
+        <f>P47*N47</f>
         <v>0.55599999999999994</v>
       </c>
-      <c r="R46" s="37"/>
-      <c r="S46" s="59"/>
-    </row>
-    <row r="47" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-      <c r="B47" s="47">
+      <c r="R47" s="37"/>
+      <c r="S47" s="59"/>
+    </row>
+    <row r="48" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="47">
         <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="C47" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D47" s="51" t="s">
+      <c r="D48" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="E47" s="51" t="s">
+      <c r="E48" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="F47" s="51" t="s">
+      <c r="F48" s="51" t="s">
         <v>128</v>
       </c>
-      <c r="G47" s="51" t="s">
+      <c r="G48" s="51" t="s">
         <v>169</v>
       </c>
-      <c r="H47" s="51" t="s">
+      <c r="H48" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="I47" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J47" s="51" t="s">
+      <c r="I48" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J48" s="51" t="s">
         <v>232</v>
       </c>
-      <c r="K47" s="51" t="s">
+      <c r="K48" s="51" t="s">
         <v>276</v>
       </c>
-      <c r="L47" s="51">
+      <c r="L48" s="51">
         <v>2</v>
       </c>
-      <c r="M47" s="51">
-        <f t="shared" ref="M47" si="37">L47*5</f>
+      <c r="M48" s="51">
+        <f t="shared" ref="M48" si="37">L48*5</f>
         <v>10</v>
       </c>
-      <c r="N47" s="51">
+      <c r="N48" s="51">
         <v>20</v>
       </c>
-      <c r="O47" s="64" t="s">
-        <v>300</v>
-      </c>
-      <c r="P47" s="52">
+      <c r="O48" s="64" t="s">
+        <v>300</v>
+      </c>
+      <c r="P48" s="52">
         <v>3.2399999999999998E-2</v>
       </c>
-      <c r="Q47" s="52">
-        <f t="shared" ref="Q47" si="38">P47*N47</f>
+      <c r="Q48" s="52">
+        <f t="shared" ref="Q48" si="38">P48*N48</f>
         <v>0.64799999999999991</v>
       </c>
-      <c r="R47" s="51"/>
-      <c r="S47" s="59"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-      <c r="B48" s="46">
-        <f>ROW(B48) - ROW($B$9)</f>
-        <v>39</v>
-      </c>
-      <c r="C48" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="E48" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="F48" s="37" t="s">
-        <v>129</v>
-      </c>
-      <c r="G48" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="H48" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="I48" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J48" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="K48" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="L48" s="37">
-        <v>3</v>
-      </c>
-      <c r="M48" s="37">
-        <f>L48*5</f>
-        <v>15</v>
-      </c>
-      <c r="N48" s="37">
-        <v>20</v>
-      </c>
-      <c r="O48" s="63" t="s">
-        <v>300</v>
-      </c>
-      <c r="P48" s="38">
-        <v>2.58E-2</v>
-      </c>
-      <c r="Q48" s="38">
-        <f>P48*N48</f>
-        <v>0.51600000000000001</v>
-      </c>
-      <c r="R48" s="37"/>
+      <c r="R48" s="51"/>
       <c r="S48" s="59"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="47">
+      <c r="B49" s="46">
+        <f>ROW(B49) - ROW($B$9)</f>
+        <v>40</v>
+      </c>
+      <c r="C49" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="F49" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="G49" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="H49" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="I49" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J49" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="K49" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="L49" s="37">
+        <v>3</v>
+      </c>
+      <c r="M49" s="37">
+        <f>L49*5</f>
+        <v>15</v>
+      </c>
+      <c r="N49" s="37">
+        <v>20</v>
+      </c>
+      <c r="O49" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="P49" s="38">
+        <v>2.58E-2</v>
+      </c>
+      <c r="Q49" s="38">
+        <f>P49*N49</f>
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="R49" s="37"/>
+      <c r="S49" s="59"/>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="47">
         <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="C49" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="51" t="s">
+      <c r="D50" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="E49" s="51" t="s">
+      <c r="E50" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="F49" s="51" t="s">
+      <c r="F50" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="G49" s="51" t="s">
+      <c r="G50" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="H49" s="51" t="s">
+      <c r="H50" s="51" t="s">
         <v>184</v>
       </c>
-      <c r="I49" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J49" s="51" t="s">
+      <c r="I50" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J50" s="51" t="s">
         <v>234</v>
       </c>
-      <c r="K49" s="51" t="s">
+      <c r="K50" s="51" t="s">
         <v>278</v>
       </c>
-      <c r="L49" s="51">
+      <c r="L50" s="51">
         <v>1</v>
       </c>
-      <c r="M49" s="51">
-        <f t="shared" ref="M49" si="39">L49*5</f>
+      <c r="M50" s="51">
+        <f t="shared" ref="M50" si="39">L50*5</f>
         <v>5</v>
       </c>
-      <c r="N49" s="51">
+      <c r="N50" s="51">
         <v>20</v>
       </c>
-      <c r="O49" s="64" t="s">
-        <v>300</v>
-      </c>
-      <c r="P49" s="52">
+      <c r="O50" s="64" t="s">
+        <v>300</v>
+      </c>
+      <c r="P50" s="52">
         <v>2.9399999999999999E-2</v>
       </c>
-      <c r="Q49" s="52">
-        <f t="shared" ref="Q49" si="40">P49*N49</f>
+      <c r="Q50" s="52">
+        <f t="shared" ref="Q50" si="40">P50*N50</f>
         <v>0.58799999999999997</v>
       </c>
-      <c r="R49" s="51"/>
-      <c r="S49" s="59"/>
-    </row>
-    <row r="50" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="B50" s="46">
-        <f>ROW(B50) - ROW($B$9)</f>
-        <v>41</v>
-      </c>
-      <c r="C50" s="53" t="s">
+      <c r="R50" s="51"/>
+      <c r="S50" s="59"/>
+    </row>
+    <row r="51" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="46">
+        <f>ROW(B51) - ROW($B$9)</f>
+        <v>42</v>
+      </c>
+      <c r="C51" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="D50" s="37" t="s">
+      <c r="D51" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="E50" s="37" t="s">
+      <c r="E51" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="F50" s="37" t="s">
+      <c r="F51" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="G50" s="37" t="s">
+      <c r="G51" s="37" t="s">
         <v>172</v>
       </c>
-      <c r="H50" s="37" t="s">
+      <c r="H51" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="I50" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J50" s="37" t="s">
+      <c r="I51" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J51" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="K50" s="37" t="s">
+      <c r="K51" s="37" t="s">
         <v>279</v>
       </c>
-      <c r="L50" s="37">
+      <c r="L51" s="37">
         <v>1</v>
       </c>
-      <c r="M50" s="37">
-        <f>L50*5</f>
+      <c r="M51" s="37">
+        <f>L51*5</f>
         <v>5</v>
       </c>
-      <c r="N50" s="37">
+      <c r="N51" s="37">
         <v>100</v>
       </c>
-      <c r="O50" s="63" t="s">
-        <v>300</v>
-      </c>
-      <c r="P50" s="38">
+      <c r="O51" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="P51" s="38">
         <v>1.9E-3</v>
       </c>
-      <c r="Q50" s="38">
-        <f>P50*N50</f>
+      <c r="Q51" s="38">
+        <f>P51*N51</f>
         <v>0.19</v>
       </c>
-      <c r="R50" s="37"/>
-      <c r="S50" s="59"/>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
-      <c r="B51" s="47">
+      <c r="R51" s="37"/>
+      <c r="S51" s="59"/>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="B52" s="47">
         <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="C51" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D51" s="51" t="s">
+      <c r="D52" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="E51" s="51" t="s">
+      <c r="E52" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="F51" s="51" t="s">
+      <c r="F52" s="51" t="s">
         <v>128</v>
       </c>
-      <c r="G51" s="51" t="s">
+      <c r="G52" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="H51" s="51" t="s">
+      <c r="H52" s="51" t="s">
         <v>184</v>
       </c>
-      <c r="I51" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J51" s="51" t="s">
+      <c r="I52" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J52" s="51" t="s">
         <v>236</v>
       </c>
-      <c r="K51" s="51" t="s">
+      <c r="K52" s="51" t="s">
         <v>280</v>
       </c>
-      <c r="L51" s="51">
+      <c r="L52" s="51">
         <v>1</v>
       </c>
-      <c r="M51" s="51">
-        <f t="shared" ref="M51" si="41">L51*5</f>
+      <c r="M52" s="51">
+        <f t="shared" ref="M52" si="41">L52*5</f>
         <v>5</v>
       </c>
-      <c r="N51" s="51">
+      <c r="N52" s="51">
         <v>20</v>
       </c>
-      <c r="O51" s="64" t="s">
-        <v>300</v>
-      </c>
-      <c r="P51" s="52">
+      <c r="O52" s="64" t="s">
+        <v>300</v>
+      </c>
+      <c r="P52" s="52">
         <v>3.8600000000000002E-2</v>
       </c>
-      <c r="Q51" s="52">
-        <f t="shared" ref="Q51" si="42">P51*N51</f>
+      <c r="Q52" s="52">
+        <f t="shared" ref="Q52" si="42">P52*N52</f>
         <v>0.77200000000000002</v>
       </c>
-      <c r="R51" s="51"/>
-      <c r="S51" s="59"/>
-    </row>
-    <row r="52" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-      <c r="B52" s="46">
-        <f>ROW(B52) - ROW($B$9)</f>
-        <v>43</v>
-      </c>
-      <c r="C52" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="E52" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="F52" s="37" t="s">
-        <v>129</v>
-      </c>
-      <c r="G52" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="H52" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="I52" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J52" s="37" t="s">
-        <v>237</v>
-      </c>
-      <c r="K52" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="L52" s="37">
-        <v>1</v>
-      </c>
-      <c r="M52" s="37">
-        <f>L52*5</f>
-        <v>5</v>
-      </c>
-      <c r="N52" s="37">
-        <v>20</v>
-      </c>
-      <c r="O52" s="63" t="s">
-        <v>300</v>
-      </c>
-      <c r="P52" s="38">
-        <v>2.1700000000000001E-2</v>
-      </c>
-      <c r="Q52" s="38">
-        <f>P52*N52</f>
-        <v>0.434</v>
-      </c>
-      <c r="R52" s="37"/>
+      <c r="R52" s="51"/>
       <c r="S52" s="59"/>
     </row>
     <row r="53" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="B53" s="47">
+      <c r="B53" s="46">
+        <f>ROW(B53) - ROW($B$9)</f>
+        <v>44</v>
+      </c>
+      <c r="C53" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="F53" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="G53" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="H53" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="I53" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J53" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="K53" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="L53" s="37">
+        <v>1</v>
+      </c>
+      <c r="M53" s="37">
+        <f>L53*5</f>
+        <v>5</v>
+      </c>
+      <c r="N53" s="37">
+        <v>20</v>
+      </c>
+      <c r="O53" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="P53" s="38">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="Q53" s="38">
+        <f>P53*N53</f>
+        <v>0.434</v>
+      </c>
+      <c r="R53" s="37"/>
+      <c r="S53" s="59"/>
+    </row>
+    <row r="54" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="B54" s="47">
         <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="C53" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="C54" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D53" s="51" t="s">
+      <c r="D54" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="E53" s="51" t="s">
+      <c r="E54" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="F53" s="51" t="s">
+      <c r="F54" s="51" t="s">
         <v>128</v>
       </c>
-      <c r="G53" s="51" t="s">
+      <c r="G54" s="51" t="s">
         <v>175</v>
       </c>
-      <c r="H53" s="51" t="s">
+      <c r="H54" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="I53" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J53" s="51" t="s">
+      <c r="I54" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J54" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="K53" s="51" t="s">
+      <c r="K54" s="51" t="s">
         <v>282</v>
       </c>
-      <c r="L53" s="51">
+      <c r="L54" s="51">
         <v>1</v>
       </c>
-      <c r="M53" s="51">
-        <f t="shared" ref="M53" si="43">L53*5</f>
+      <c r="M54" s="51">
+        <f t="shared" ref="M54" si="43">L54*5</f>
         <v>5</v>
       </c>
-      <c r="N53" s="51">
+      <c r="N54" s="51">
         <v>20</v>
       </c>
-      <c r="O53" s="64" t="s">
-        <v>300</v>
-      </c>
-      <c r="P53" s="52">
+      <c r="O54" s="64" t="s">
+        <v>300</v>
+      </c>
+      <c r="P54" s="52">
         <v>3.1199999999999999E-2</v>
       </c>
-      <c r="Q53" s="52">
-        <f t="shared" ref="Q53" si="44">P53*N53</f>
+      <c r="Q54" s="52">
+        <f t="shared" ref="Q54" si="44">P54*N54</f>
         <v>0.624</v>
       </c>
-      <c r="R53" s="51"/>
-      <c r="S53" s="59"/>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
-      <c r="B54" s="46">
-        <f>ROW(B54) - ROW($B$9)</f>
-        <v>45</v>
-      </c>
-      <c r="C54" s="53" t="s">
+      <c r="R54" s="51"/>
+      <c r="S54" s="59"/>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A55" s="1"/>
+      <c r="B55" s="46">
+        <f>ROW(B55) - ROW($B$9)</f>
+        <v>46</v>
+      </c>
+      <c r="C55" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="D54" s="37" t="s">
+      <c r="D55" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="E54" s="37" t="s">
+      <c r="E55" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="F54" s="37" t="s">
+      <c r="F55" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="G54" s="37" t="s">
+      <c r="G55" s="37" t="s">
         <v>176</v>
       </c>
-      <c r="H54" s="37" t="s">
+      <c r="H55" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I54" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J54" s="37" t="s">
+      <c r="I55" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J55" s="37" t="s">
         <v>239</v>
       </c>
-      <c r="K54" s="37" t="s">
+      <c r="K55" s="37" t="s">
         <v>283</v>
       </c>
-      <c r="L54" s="37">
+      <c r="L55" s="37">
         <v>1</v>
       </c>
-      <c r="M54" s="37">
-        <f>L54*5</f>
+      <c r="M55" s="37">
+        <f>L55*5</f>
         <v>5</v>
       </c>
-      <c r="N54" s="37">
+      <c r="N55" s="37">
         <v>20</v>
       </c>
-      <c r="O54" s="63" t="s">
-        <v>300</v>
-      </c>
-      <c r="P54" s="38">
+      <c r="O55" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="P55" s="38">
         <v>2.52E-2</v>
       </c>
-      <c r="Q54" s="38">
-        <f>P54*N54</f>
+      <c r="Q55" s="38">
+        <f>P55*N55</f>
         <v>0.504</v>
       </c>
-      <c r="R54" s="37"/>
-      <c r="S54" s="59"/>
-    </row>
-    <row r="55" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A55" s="1"/>
-      <c r="B55" s="47">
+      <c r="R55" s="37"/>
+      <c r="S55" s="59"/>
+    </row>
+    <row r="56" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A56" s="1"/>
+      <c r="B56" s="47">
         <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="C55" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="C56" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D55" s="51" t="s">
+      <c r="D56" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="E55" s="51" t="s">
+      <c r="E56" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="F55" s="51" t="s">
+      <c r="F56" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="G55" s="51" t="s">
+      <c r="G56" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="H55" s="51" t="s">
+      <c r="H56" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="I55" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J55" s="51" t="s">
+      <c r="I56" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J56" s="51" t="s">
         <v>240</v>
       </c>
-      <c r="K55" s="51" t="s">
+      <c r="K56" s="51" t="s">
         <v>284</v>
       </c>
-      <c r="L55" s="51">
+      <c r="L56" s="51">
         <v>1</v>
       </c>
-      <c r="M55" s="51">
-        <f t="shared" ref="M55" si="45">L55*5</f>
+      <c r="M56" s="51">
+        <f t="shared" ref="M56" si="45">L56*5</f>
         <v>5</v>
       </c>
-      <c r="N55" s="51">
+      <c r="N56" s="51">
         <v>20</v>
       </c>
-      <c r="O55" s="64" t="s">
-        <v>300</v>
-      </c>
-      <c r="P55" s="52">
+      <c r="O56" s="64" t="s">
+        <v>300</v>
+      </c>
+      <c r="P56" s="52">
         <v>2.3699999999999999E-2</v>
       </c>
-      <c r="Q55" s="52">
-        <f t="shared" ref="Q55" si="46">P55*N55</f>
+      <c r="Q56" s="52">
+        <f t="shared" ref="Q56" si="46">P56*N56</f>
         <v>0.47399999999999998</v>
       </c>
-      <c r="R55" s="51"/>
-      <c r="S55" s="59"/>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A56" s="1"/>
-      <c r="B56" s="46">
-        <f>ROW(B56) - ROW($B$9)</f>
-        <v>47</v>
-      </c>
-      <c r="C56" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="E56" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="F56" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="G56" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="H56" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="I56" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J56" s="37" t="s">
-        <v>241</v>
-      </c>
-      <c r="K56" s="37" t="s">
-        <v>285</v>
-      </c>
-      <c r="L56" s="37">
-        <v>2</v>
-      </c>
-      <c r="M56" s="37">
-        <f>L56*5</f>
-        <v>10</v>
-      </c>
-      <c r="N56" s="37">
-        <v>20</v>
-      </c>
-      <c r="O56" s="63" t="s">
-        <v>300</v>
-      </c>
-      <c r="P56" s="38">
-        <v>2.5399999999999999E-2</v>
-      </c>
-      <c r="Q56" s="38">
-        <f>P56*N56</f>
-        <v>0.50800000000000001</v>
-      </c>
-      <c r="R56" s="37"/>
+      <c r="R56" s="51"/>
       <c r="S56" s="59"/>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
-      <c r="B57" s="47">
+      <c r="B57" s="46">
+        <f>ROW(B57) - ROW($B$9)</f>
+        <v>48</v>
+      </c>
+      <c r="C57" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="F57" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="G57" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="H57" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="I57" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J57" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="K57" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="L57" s="37">
+        <v>2</v>
+      </c>
+      <c r="M57" s="37">
+        <f>L57*5</f>
+        <v>10</v>
+      </c>
+      <c r="N57" s="37">
+        <v>20</v>
+      </c>
+      <c r="O57" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="P57" s="38">
+        <v>2.5399999999999999E-2</v>
+      </c>
+      <c r="Q57" s="38">
+        <f>P57*N57</f>
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="R57" s="37"/>
+      <c r="S57" s="59"/>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+      <c r="B58" s="47">
         <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="C57" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C58" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="D57" s="60" t="s">
+      <c r="D58" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="E57" s="60" t="s">
+      <c r="E58" s="60" t="s">
         <v>116</v>
       </c>
-      <c r="F57" s="60" t="s">
+      <c r="F58" s="60" t="s">
         <v>298</v>
       </c>
-      <c r="G57" s="60" t="s">
+      <c r="G58" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H57" s="60" t="s">
-        <v>301</v>
-      </c>
-      <c r="I57" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J57" s="60" t="s">
-        <v>301</v>
-      </c>
-      <c r="K57" s="60" t="s">
-        <v>301</v>
-      </c>
-      <c r="L57" s="60">
+      <c r="H58" s="60" t="s">
+        <v>301</v>
+      </c>
+      <c r="I58" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J58" s="60" t="s">
+        <v>301</v>
+      </c>
+      <c r="K58" s="60" t="s">
+        <v>301</v>
+      </c>
+      <c r="L58" s="60">
         <v>2</v>
       </c>
-      <c r="M57" s="60">
-        <f t="shared" ref="M57" si="47">L57*5</f>
+      <c r="M58" s="60">
+        <f t="shared" ref="M58" si="47">L58*5</f>
         <v>10</v>
       </c>
-      <c r="N57" s="60" t="s">
-        <v>301</v>
-      </c>
-      <c r="O57" s="60" t="s">
-        <v>301</v>
-      </c>
-      <c r="P57" s="61" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q57" s="61" t="s">
-        <v>301</v>
-      </c>
-      <c r="R57" s="60"/>
-      <c r="S57" s="62"/>
-    </row>
-    <row r="58" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A58" s="1"/>
-      <c r="B58" s="46">
-        <f>ROW(B58) - ROW($B$9)</f>
-        <v>49</v>
-      </c>
-      <c r="C58" s="53" t="s">
+      <c r="N58" s="60" t="s">
+        <v>301</v>
+      </c>
+      <c r="O58" s="60" t="s">
+        <v>301</v>
+      </c>
+      <c r="P58" s="61" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q58" s="61" t="s">
+        <v>301</v>
+      </c>
+      <c r="R58" s="60"/>
+      <c r="S58" s="62"/>
+    </row>
+    <row r="59" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A59" s="1"/>
+      <c r="B59" s="46">
+        <f>ROW(B59) - ROW($B$9)</f>
+        <v>50</v>
+      </c>
+      <c r="C59" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="D58" s="37" t="s">
+      <c r="D59" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="E58" s="37" t="s">
+      <c r="E59" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="F58" s="37" t="s">
+      <c r="F59" s="37" t="s">
         <v>298</v>
       </c>
-      <c r="G58" s="37" t="s">
+      <c r="G59" s="37" t="s">
         <v>179</v>
       </c>
-      <c r="H58" s="37" t="s">
+      <c r="H59" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="I58" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J58" s="37" t="s">
+      <c r="I59" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J59" s="37" t="s">
         <v>242</v>
       </c>
-      <c r="K58" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="L58" s="37">
+      <c r="K59" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="L59" s="37">
         <v>9</v>
       </c>
-      <c r="M58" s="37">
-        <f>L58*5</f>
+      <c r="M59" s="37">
+        <f>L59*5</f>
         <v>45</v>
       </c>
-      <c r="N58" s="37">
+      <c r="N59" s="37">
         <v>47</v>
       </c>
-      <c r="O58" s="63" t="s">
-        <v>300</v>
-      </c>
-      <c r="P58" s="38">
+      <c r="O59" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="P59" s="38">
         <v>0.46460000000000001</v>
       </c>
-      <c r="Q58" s="38">
-        <f>P58*N58</f>
+      <c r="Q59" s="38">
+        <f>P59*N59</f>
         <v>21.836200000000002</v>
       </c>
-      <c r="R58" s="37"/>
-      <c r="S58" s="59"/>
-    </row>
-    <row r="59" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="1"/>
-      <c r="B59" s="47">
+      <c r="R59" s="37"/>
+      <c r="S59" s="59"/>
+    </row>
+    <row r="60" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="1"/>
+      <c r="B60" s="47">
         <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="C59" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C60" s="54" t="s">
         <v>312</v>
       </c>
-      <c r="D59" s="51" t="s">
+      <c r="D60" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="E59" s="51" t="s">
+      <c r="E60" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="F59" s="51" t="s">
+      <c r="F60" s="51" t="s">
         <v>130</v>
       </c>
-      <c r="G59" s="51" t="s">
+      <c r="G60" s="51" t="s">
         <v>180</v>
       </c>
-      <c r="H59" s="51" t="s">
+      <c r="H60" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="I59" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="J59" s="51" t="s">
+      <c r="I60" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="J60" s="51" t="s">
         <v>299</v>
       </c>
-      <c r="K59" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="L59" s="51">
+      <c r="K60" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="L60" s="51">
         <v>3</v>
       </c>
-      <c r="M59" s="51">
-        <f t="shared" ref="M59" si="48">L59*5</f>
+      <c r="M60" s="51">
+        <f t="shared" ref="M60" si="48">L60*5</f>
         <v>15</v>
       </c>
-      <c r="N59" s="51">
+      <c r="N60" s="51">
         <v>20</v>
       </c>
-      <c r="O59" s="64" t="s">
-        <v>300</v>
-      </c>
-      <c r="P59" s="52">
+      <c r="O60" s="64" t="s">
+        <v>300</v>
+      </c>
+      <c r="P60" s="52">
         <v>0.1139</v>
       </c>
-      <c r="Q59" s="52">
-        <f t="shared" ref="Q59" si="49">P59*N59</f>
+      <c r="Q60" s="52">
+        <f t="shared" ref="Q60" si="49">P60*N60</f>
         <v>2.278</v>
       </c>
-      <c r="R59" s="51"/>
-      <c r="S59" s="39"/>
-    </row>
-    <row r="60" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="1"/>
-      <c r="B60" s="40"/>
-      <c r="C60" s="41"/>
-      <c r="D60" s="42"/>
-      <c r="E60" s="43"/>
-      <c r="F60" s="44"/>
-      <c r="G60" s="45"/>
-      <c r="H60" s="44"/>
-      <c r="I60" s="45"/>
-      <c r="J60" s="44"/>
-      <c r="K60" s="45"/>
-      <c r="L60" s="45"/>
-      <c r="M60" s="45"/>
-      <c r="N60" s="81" t="s">
-        <v>5</v>
-      </c>
-      <c r="O60" s="82"/>
-      <c r="P60" s="82"/>
-      <c r="Q60" s="48">
-        <f>SUM(Q10:Q59)</f>
-        <v>59.918100000000003</v>
-      </c>
-      <c r="R60" s="83"/>
-      <c r="S60" s="84"/>
+      <c r="R60" s="51"/>
+      <c r="S60" s="39"/>
     </row>
     <row r="61" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="10"/>
-      <c r="M61" s="10"/>
-      <c r="N61" s="81" t="s">
+      <c r="B61" s="40"/>
+      <c r="C61" s="41"/>
+      <c r="D61" s="42"/>
+      <c r="E61" s="43"/>
+      <c r="F61" s="44"/>
+      <c r="G61" s="45"/>
+      <c r="H61" s="44"/>
+      <c r="I61" s="45"/>
+      <c r="J61" s="44"/>
+      <c r="K61" s="45"/>
+      <c r="L61" s="45"/>
+      <c r="M61" s="45"/>
+      <c r="N61" s="91" t="s">
+        <v>5</v>
+      </c>
+      <c r="O61" s="92"/>
+      <c r="P61" s="92"/>
+      <c r="Q61" s="48">
+        <f>SUM(Q10:Q60)</f>
+        <v>64.320099999999982</v>
+      </c>
+      <c r="R61" s="95"/>
+      <c r="S61" s="96"/>
+    </row>
+    <row r="62" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="1"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="10"/>
+      <c r="I62" s="10"/>
+      <c r="J62" s="10"/>
+      <c r="K62" s="10"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="O61" s="82"/>
-      <c r="P61" s="82"/>
-      <c r="Q61" s="49">
-        <f>Q60/5</f>
-        <v>11.98362</v>
-      </c>
-      <c r="R61" s="85"/>
-      <c r="S61" s="86"/>
+      <c r="O62" s="92"/>
+      <c r="P62" s="92"/>
+      <c r="Q62" s="49">
+        <f>Q61/5</f>
+        <v>12.864019999999996</v>
+      </c>
+      <c r="R62" s="97"/>
+      <c r="S62" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R60:S61"/>
-    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="R61:S62"/>
     <mergeCell ref="N61:P61"/>
+    <mergeCell ref="N62:P62"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -11426,46 +11522,47 @@
     <hyperlink ref="O24" r:id="rId10" display="lCSC"/>
     <hyperlink ref="O25" r:id="rId11"/>
     <hyperlink ref="O26" r:id="rId12"/>
-    <hyperlink ref="O27" r:id="rId13"/>
-    <hyperlink ref="O28" r:id="rId14"/>
-    <hyperlink ref="O29" r:id="rId15"/>
-    <hyperlink ref="O30" r:id="rId16"/>
-    <hyperlink ref="O31" r:id="rId17"/>
-    <hyperlink ref="O32" r:id="rId18"/>
-    <hyperlink ref="O33" r:id="rId19"/>
-    <hyperlink ref="O34" r:id="rId20"/>
-    <hyperlink ref="O35" r:id="rId21"/>
-    <hyperlink ref="O36" r:id="rId22"/>
-    <hyperlink ref="O37" r:id="rId23"/>
-    <hyperlink ref="O38" r:id="rId24"/>
-    <hyperlink ref="O39" r:id="rId25"/>
-    <hyperlink ref="O40" r:id="rId26"/>
-    <hyperlink ref="O41" r:id="rId27"/>
-    <hyperlink ref="O42" r:id="rId28"/>
-    <hyperlink ref="O43" r:id="rId29"/>
-    <hyperlink ref="O44" r:id="rId30"/>
-    <hyperlink ref="O45" r:id="rId31"/>
-    <hyperlink ref="O46" r:id="rId32"/>
-    <hyperlink ref="O47" r:id="rId33"/>
-    <hyperlink ref="O48" r:id="rId34"/>
-    <hyperlink ref="O49" r:id="rId35"/>
-    <hyperlink ref="O50" r:id="rId36"/>
-    <hyperlink ref="O51" r:id="rId37"/>
-    <hyperlink ref="O52" r:id="rId38"/>
-    <hyperlink ref="O53" r:id="rId39"/>
-    <hyperlink ref="O54" r:id="rId40"/>
-    <hyperlink ref="O55" r:id="rId41"/>
-    <hyperlink ref="O56" r:id="rId42"/>
-    <hyperlink ref="O58" r:id="rId43"/>
-    <hyperlink ref="O59" r:id="rId44"/>
-    <hyperlink ref="O18" r:id="rId45"/>
-    <hyperlink ref="O16" r:id="rId46"/>
-    <hyperlink ref="O21" r:id="rId47"/>
-    <hyperlink ref="O22" r:id="rId48"/>
-    <hyperlink ref="O13" r:id="rId49"/>
+    <hyperlink ref="O28" r:id="rId13"/>
+    <hyperlink ref="O29" r:id="rId14"/>
+    <hyperlink ref="O30" r:id="rId15"/>
+    <hyperlink ref="O31" r:id="rId16"/>
+    <hyperlink ref="O32" r:id="rId17"/>
+    <hyperlink ref="O34" r:id="rId18"/>
+    <hyperlink ref="O35" r:id="rId19"/>
+    <hyperlink ref="O36" r:id="rId20"/>
+    <hyperlink ref="O37" r:id="rId21"/>
+    <hyperlink ref="O38" r:id="rId22"/>
+    <hyperlink ref="O39" r:id="rId23"/>
+    <hyperlink ref="O40" r:id="rId24"/>
+    <hyperlink ref="O41" r:id="rId25"/>
+    <hyperlink ref="O42" r:id="rId26"/>
+    <hyperlink ref="O43" r:id="rId27"/>
+    <hyperlink ref="O44" r:id="rId28"/>
+    <hyperlink ref="O45" r:id="rId29"/>
+    <hyperlink ref="O46" r:id="rId30"/>
+    <hyperlink ref="O47" r:id="rId31"/>
+    <hyperlink ref="O48" r:id="rId32"/>
+    <hyperlink ref="O49" r:id="rId33"/>
+    <hyperlink ref="O50" r:id="rId34"/>
+    <hyperlink ref="O51" r:id="rId35"/>
+    <hyperlink ref="O52" r:id="rId36"/>
+    <hyperlink ref="O53" r:id="rId37"/>
+    <hyperlink ref="O54" r:id="rId38"/>
+    <hyperlink ref="O55" r:id="rId39"/>
+    <hyperlink ref="O56" r:id="rId40"/>
+    <hyperlink ref="O57" r:id="rId41"/>
+    <hyperlink ref="O59" r:id="rId42"/>
+    <hyperlink ref="O60" r:id="rId43"/>
+    <hyperlink ref="O18" r:id="rId44"/>
+    <hyperlink ref="O16" r:id="rId45"/>
+    <hyperlink ref="O21" r:id="rId46"/>
+    <hyperlink ref="O22" r:id="rId47"/>
+    <hyperlink ref="O13" r:id="rId48"/>
+    <hyperlink ref="O27" r:id="rId49"/>
+    <hyperlink ref="O33" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId50"/>
-  <drawing r:id="rId51"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId51"/>
+  <drawing r:id="rId52"/>
 </worksheet>
 </file>
--- a/Design Files/Xponent-tech/BOM/eSpark-BOM-Xponent-tech.xlsx
+++ b/Design Files/Xponent-tech/BOM/eSpark-BOM-Xponent-tech.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="1 Board" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="328">
   <si>
     <t>Component list</t>
   </si>
@@ -4898,7 +4898,7 @@
       <c r="Q56" s="37"/>
       <c r="R56" s="59"/>
     </row>
-    <row r="57" spans="1:18" s="68" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" s="68" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A57" s="66"/>
       <c r="B57" s="47">
         <f t="shared" si="0"/>
@@ -4941,8 +4941,9 @@
       <c r="O57" s="38">
         <v>0.14399999999999999</v>
       </c>
-      <c r="P57" s="61" t="s">
-        <v>298</v>
+      <c r="P57" s="38">
+        <f>O57*M57</f>
+        <v>0.72</v>
       </c>
       <c r="Q57" s="60"/>
       <c r="R57" s="62"/>
@@ -5172,7 +5173,7 @@
       <c r="O62" s="97"/>
       <c r="P62" s="48">
         <f>SUM(P10:P61)</f>
-        <v>38.397500000000001</v>
+        <v>39.1175</v>
       </c>
       <c r="Q62" s="78"/>
       <c r="R62" s="91"/>

--- a/Design Files/Xponent-tech/BOM/eSpark-BOM-Xponent-tech.xlsx
+++ b/Design Files/Xponent-tech/BOM/eSpark-BOM-Xponent-tech.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="328">
   <si>
     <t>Component list</t>
   </si>
@@ -4126,7 +4126,9 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="54"/>
+      <c r="C42" s="53" t="s">
+        <v>12</v>
+      </c>
       <c r="D42" s="80" t="s">
         <v>46</v>
       </c>
@@ -7306,7 +7308,9 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="54"/>
+      <c r="C42" s="53" t="s">
+        <v>12</v>
+      </c>
       <c r="D42" s="80" t="s">
         <v>46</v>
       </c>
@@ -10593,7 +10597,9 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="54"/>
+      <c r="C42" s="53" t="s">
+        <v>12</v>
+      </c>
       <c r="D42" s="80" t="s">
         <v>46</v>
       </c>
